--- a/ky/downloads/data-excel/4.1.1.a.xlsx
+++ b/ky/downloads/data-excel/4.1.1.a.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CE6B01-8DFD-4BDF-9805-10C4009137A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -14,13 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="69">
-  <si>
-    <t xml:space="preserve">4.1.1.1а Жалпы билим берүү уюмдарынын сабактарына барбай калган балдардын жана 7-17 жаштагы (1-11-класстардагы) өспүрүмдөрдүн  себептер жана жынысы боюнча саны </t>
-  </si>
-  <si>
-    <t>4.1.1.1а Number of children (1-11 classes)  not started studies at school by cause,  sex and territory</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="69">
   <si>
     <t xml:space="preserve">                           (адам)</t>
   </si>
@@ -221,14 +216,20 @@
     <t>Note : Data on the floor began to be developed from 2005 .</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1.1.1а Численность детей и подростков 7-17 лет (1-11классов), не приступивших  к занятиям в общеобразовательные организации по причинам,  по полу </t>
+    <t xml:space="preserve">4.1.1а Жалпы билим берүү уюмдарынын сабактарына барбай калган балдардын жана 7-17 жаштагы (1-11-класстардагы) өспүрүмдөрдүн  себептер жана жынысы боюнча саны </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1.1а Численность детей и подростков 7-17 лет (1-11классов), не приступивших  к занятиям в общеобразовательные организации по причинам,  по полу </t>
+  </si>
+  <si>
+    <t>4.1.1а Number of children (1-11 classes)  not started studies at school by cause,  sex and territory</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,6 +353,17 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Times New Roman Cyr"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -390,67 +402,69 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -459,19 +473,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -480,19 +491,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -501,15 +509,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -531,38 +530,58 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Normal_PPI" xfId="3" xr:uid="{BF16A917-5272-41F0-AE00-FA3880BE070D}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный_ССП Социальный" xfId="1"/>
+    <cellStyle name="Обычный 2" xfId="2" xr:uid="{20694DEF-E751-4055-A077-1E1D43150C47}"/>
+    <cellStyle name="Обычный_ССП Социальный" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -578,9 +597,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -618,9 +637,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -655,7 +674,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -690,7 +709,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -863,8 +882,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="39.42578125" customWidth="1"/>
@@ -873,15 +892,15 @@
     <col min="9" max="9" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -899,15 +918,15 @@
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>4</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -925,7 +944,7 @@
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -944,20 +963,21 @@
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
-      <c r="S3" s="54"/>
-      <c r="T3" s="54"/>
-      <c r="U3" s="54"/>
-      <c r="V3" s="54"/>
-    </row>
-    <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="W3" s="54"/>
+    </row>
+    <row r="4" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>5</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>7</v>
       </c>
       <c r="D4" s="15">
         <v>2005</v>
@@ -1004,28 +1024,31 @@
       <c r="R4" s="15">
         <v>2019</v>
       </c>
-      <c r="S4" s="48">
+      <c r="S4" s="43">
         <v>2020</v>
       </c>
-      <c r="T4" s="48">
+      <c r="T4" s="43">
         <v>2021</v>
       </c>
-      <c r="U4" s="48">
+      <c r="U4" s="43">
         <v>2022</v>
       </c>
-      <c r="V4" s="48">
+      <c r="V4" s="43">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W4" s="55">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>10</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
@@ -1042,22 +1065,23 @@
       <c r="P5" s="19"/>
       <c r="Q5" s="19"/>
       <c r="R5" s="19"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
-    </row>
-    <row r="6" spans="1:22" ht="24" x14ac:dyDescent="0.25">
+      <c r="S5" s="44"/>
+      <c r="T5" s="44"/>
+      <c r="U5" s="44"/>
+      <c r="V5" s="44"/>
+      <c r="W5" s="50"/>
+    </row>
+    <row r="6" spans="1:23" ht="24" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="23">
+      <c r="D6" s="22">
         <v>2331</v>
       </c>
       <c r="E6" s="14">
@@ -1066,96 +1090,100 @@
       <c r="F6" s="14">
         <v>2050</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="23">
         <v>1833</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="23">
         <v>1813</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="23">
         <v>2178</v>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="23">
         <v>2406</v>
       </c>
-      <c r="K6" s="24">
+      <c r="K6" s="23">
         <v>1920</v>
       </c>
-      <c r="L6" s="24">
+      <c r="L6" s="23">
         <v>1708</v>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="24">
         <v>1453</v>
       </c>
-      <c r="N6" s="25">
+      <c r="N6" s="24">
         <v>1254</v>
       </c>
-      <c r="O6" s="26">
+      <c r="O6" s="25">
         <v>1469</v>
       </c>
-      <c r="P6" s="26">
+      <c r="P6" s="25">
         <v>1464</v>
       </c>
-      <c r="Q6" s="24">
+      <c r="Q6" s="23">
         <v>1622</v>
       </c>
-      <c r="R6" s="24">
+      <c r="R6" s="23">
         <v>1662</v>
       </c>
-      <c r="S6" s="50">
+      <c r="S6" s="45">
         <v>1570</v>
       </c>
-      <c r="T6" s="55">
+      <c r="T6" s="49">
         <v>1466</v>
       </c>
-      <c r="U6" s="55">
+      <c r="U6" s="49">
         <v>1456</v>
       </c>
-      <c r="V6" s="55">
+      <c r="V6" s="49">
         <v>1332</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="W6" s="56">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="30"/>
+      <c r="D7" s="29"/>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="18"/>
       <c r="N7" s="18"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="52"/>
-      <c r="U7" s="52"/>
-      <c r="V7" s="52"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="33"/>
+      <c r="T7" s="46"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="46"/>
+      <c r="W7" s="52"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <v>295</v>
       </c>
       <c r="E8" s="18">
@@ -1164,66 +1192,69 @@
       <c r="F8" s="18">
         <v>154</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="27">
         <v>168</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="27">
         <v>94</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="27">
         <v>85</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="27">
         <v>226</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="27">
         <v>157</v>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="27">
         <v>55</v>
       </c>
       <c r="M8" s="18">
         <v>80</v>
       </c>
-      <c r="N8" s="32">
+      <c r="N8" s="30">
         <v>80</v>
       </c>
-      <c r="O8" s="33">
+      <c r="O8" s="31">
         <v>84</v>
       </c>
-      <c r="P8" s="33">
+      <c r="P8" s="31">
         <v>99</v>
       </c>
-      <c r="Q8" s="31">
+      <c r="Q8" s="27">
         <v>104</v>
       </c>
-      <c r="R8" s="31">
+      <c r="R8" s="27">
         <v>152</v>
       </c>
-      <c r="S8" s="51">
+      <c r="S8" s="33">
         <v>115</v>
       </c>
-      <c r="T8" s="52">
+      <c r="T8" s="46">
         <v>76</v>
       </c>
-      <c r="U8" s="52">
+      <c r="U8" s="46">
         <v>45</v>
       </c>
-      <c r="V8" s="52">
+      <c r="V8" s="46">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="W8" s="52">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <v>86</v>
       </c>
       <c r="E9" s="18">
@@ -1232,134 +1263,140 @@
       <c r="F9" s="18">
         <v>116</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="27">
         <v>74</v>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="27">
         <v>55</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="27">
         <v>151</v>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="27">
         <v>72</v>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="27">
         <v>27</v>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="27">
         <v>32</v>
       </c>
       <c r="M9" s="18">
         <v>3</v>
       </c>
-      <c r="N9" s="32">
+      <c r="N9" s="30">
         <v>16</v>
       </c>
-      <c r="O9" s="33">
+      <c r="O9" s="31">
         <v>17</v>
       </c>
-      <c r="P9" s="33">
-        <v>24</v>
-      </c>
-      <c r="Q9" s="31">
+      <c r="P9" s="31">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="27">
         <v>39</v>
       </c>
-      <c r="R9" s="31">
+      <c r="R9" s="27">
         <v>4</v>
       </c>
-      <c r="S9" s="51">
+      <c r="S9" s="33">
         <v>27</v>
       </c>
-      <c r="T9" s="52">
+      <c r="T9" s="46">
         <v>15</v>
       </c>
-      <c r="U9" s="52">
+      <c r="U9" s="46">
         <v>35</v>
       </c>
-      <c r="V9" s="52">
+      <c r="V9" s="46">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
+      <c r="W9" s="52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="24" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>25</v>
-      </c>
       <c r="D10" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" s="31">
+        <v>24</v>
+      </c>
+      <c r="L10" s="27">
         <v>3</v>
       </c>
       <c r="M10" s="18">
         <v>1</v>
       </c>
-      <c r="N10" s="32">
+      <c r="N10" s="30">
         <v>8</v>
       </c>
-      <c r="O10" s="33">
+      <c r="O10" s="31">
         <v>3</v>
       </c>
-      <c r="P10" s="32" t="s">
+      <c r="P10" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" s="27">
+        <v>4</v>
+      </c>
+      <c r="R10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="S10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="T10" s="46">
+        <v>1</v>
+      </c>
+      <c r="U10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="V10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="W10" s="52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="Q10" s="31">
-        <v>4</v>
-      </c>
-      <c r="R10" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S10" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="T10" s="52">
-        <v>1</v>
-      </c>
-      <c r="U10" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="V10" s="52" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="C11" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="30">
+      <c r="D11" s="29">
         <v>208</v>
       </c>
       <c r="E11" s="18">
@@ -1368,66 +1405,69 @@
       <c r="F11" s="18">
         <v>175</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="27">
         <v>540</v>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="27">
         <v>321</v>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="27">
         <v>287</v>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="27">
         <v>466</v>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="27">
         <v>414</v>
       </c>
-      <c r="L11" s="31">
+      <c r="L11" s="27">
         <v>147</v>
       </c>
       <c r="M11" s="18">
         <v>359</v>
       </c>
-      <c r="N11" s="32">
+      <c r="N11" s="30">
         <v>175</v>
       </c>
-      <c r="O11" s="33">
+      <c r="O11" s="31">
         <v>287</v>
       </c>
-      <c r="P11" s="33">
+      <c r="P11" s="31">
         <v>320</v>
       </c>
-      <c r="Q11" s="31">
+      <c r="Q11" s="27">
         <v>400</v>
       </c>
-      <c r="R11" s="31">
+      <c r="R11" s="27">
         <v>374</v>
       </c>
-      <c r="S11" s="51">
+      <c r="S11" s="33">
         <v>271</v>
       </c>
-      <c r="T11" s="52">
+      <c r="T11" s="46">
         <v>188</v>
       </c>
-      <c r="U11" s="52">
+      <c r="U11" s="46">
         <v>217</v>
       </c>
-      <c r="V11" s="52">
+      <c r="V11" s="46">
         <v>163</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
+      <c r="W11" s="52">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="30">
+      <c r="D12" s="29">
         <v>222</v>
       </c>
       <c r="E12" s="18">
@@ -1436,66 +1476,69 @@
       <c r="F12" s="18">
         <v>127</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="27">
         <v>123</v>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="27">
         <v>124</v>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="27">
         <v>203</v>
       </c>
-      <c r="J12" s="31">
+      <c r="J12" s="27">
         <v>131</v>
       </c>
-      <c r="K12" s="31">
+      <c r="K12" s="27">
         <v>115</v>
       </c>
-      <c r="L12" s="31">
+      <c r="L12" s="27">
         <v>69</v>
       </c>
       <c r="M12" s="18">
         <v>61</v>
       </c>
-      <c r="N12" s="32">
+      <c r="N12" s="30">
         <v>38</v>
       </c>
-      <c r="O12" s="33">
+      <c r="O12" s="31">
         <v>26</v>
       </c>
-      <c r="P12" s="33">
+      <c r="P12" s="31">
         <v>29</v>
       </c>
-      <c r="Q12" s="31">
+      <c r="Q12" s="27">
         <v>66</v>
       </c>
-      <c r="R12" s="31">
+      <c r="R12" s="27">
         <v>34</v>
       </c>
-      <c r="S12" s="51">
+      <c r="S12" s="33">
         <v>39</v>
       </c>
-      <c r="T12" s="52">
+      <c r="T12" s="46">
         <v>22</v>
       </c>
-      <c r="U12" s="52">
+      <c r="U12" s="46">
         <v>22</v>
       </c>
-      <c r="V12" s="52">
+      <c r="V12" s="46">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="W12" s="52">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="30">
+      <c r="D13" s="29">
         <v>87</v>
       </c>
       <c r="E13" s="18">
@@ -1504,66 +1547,69 @@
       <c r="F13" s="18">
         <v>72</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="27">
         <v>64</v>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="27">
         <v>15</v>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="27">
         <v>27</v>
       </c>
-      <c r="J13" s="31">
+      <c r="J13" s="27">
         <v>40</v>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="27">
         <v>23</v>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="27">
         <v>14</v>
       </c>
       <c r="M13" s="18">
         <v>7</v>
       </c>
-      <c r="N13" s="32">
+      <c r="N13" s="30">
         <v>8</v>
       </c>
-      <c r="O13" s="33">
+      <c r="O13" s="31">
         <v>8</v>
       </c>
-      <c r="P13" s="33">
+      <c r="P13" s="31">
         <v>9</v>
       </c>
-      <c r="Q13" s="31">
+      <c r="Q13" s="27">
         <v>12</v>
       </c>
-      <c r="R13" s="31">
+      <c r="R13" s="27">
         <v>13</v>
       </c>
-      <c r="S13" s="51">
+      <c r="S13" s="33">
         <v>8</v>
       </c>
-      <c r="T13" s="52">
+      <c r="T13" s="46">
         <v>15</v>
       </c>
-      <c r="U13" s="52">
+      <c r="U13" s="46">
         <v>8</v>
       </c>
-      <c r="V13" s="52">
+      <c r="V13" s="46">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
+      <c r="W13" s="52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="30">
+      <c r="D14" s="29">
         <v>11</v>
       </c>
       <c r="E14" s="18">
@@ -1572,134 +1618,140 @@
       <c r="F14" s="18">
         <v>1</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="27">
         <v>3</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="27">
         <v>16</v>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="27">
         <v>9</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="27">
         <v>4</v>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="27">
         <v>4</v>
       </c>
-      <c r="L14" s="31">
+      <c r="L14" s="27">
         <v>6</v>
       </c>
       <c r="M14" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="N14" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="O14" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="P14" s="32" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="N14" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="P14" s="30" t="s">
+        <v>24</v>
       </c>
       <c r="Q14" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="R14" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S14" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="T14" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="U14" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="V14" s="52" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="S14" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="T14" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="U14" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="V14" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="W14" s="52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="24" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>41</v>
-      </c>
       <c r="D15" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L15" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M15" s="18">
         <v>3</v>
       </c>
-      <c r="N15" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="P15" s="32" t="s">
-        <v>26</v>
+      <c r="N15" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="P15" s="30" t="s">
+        <v>24</v>
       </c>
       <c r="Q15" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="R15" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S15" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="V15" s="52" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="S15" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="T15" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="U15" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="V15" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="W15" s="52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="30">
+      <c r="D16" s="29">
         <v>102</v>
       </c>
       <c r="E16" s="18">
@@ -1708,336 +1760,351 @@
       <c r="F16" s="18">
         <v>204</v>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="27">
         <v>79</v>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="27">
         <v>185</v>
       </c>
-      <c r="I16" s="31">
+      <c r="I16" s="27">
         <v>183</v>
       </c>
-      <c r="J16" s="31">
+      <c r="J16" s="27">
         <v>211</v>
       </c>
-      <c r="K16" s="31">
+      <c r="K16" s="27">
         <v>136</v>
       </c>
-      <c r="L16" s="31">
+      <c r="L16" s="27">
         <v>641</v>
       </c>
       <c r="M16" s="18">
         <v>114</v>
       </c>
-      <c r="N16" s="32">
+      <c r="N16" s="30">
         <v>89</v>
       </c>
-      <c r="O16" s="33">
+      <c r="O16" s="31">
         <v>241</v>
       </c>
-      <c r="P16" s="33">
+      <c r="P16" s="31">
         <v>218</v>
       </c>
-      <c r="Q16" s="31">
+      <c r="Q16" s="27">
         <v>108</v>
       </c>
-      <c r="R16" s="31">
+      <c r="R16" s="27">
         <v>121</v>
       </c>
-      <c r="S16" s="51">
+      <c r="S16" s="33">
         <v>93</v>
       </c>
-      <c r="T16" s="52">
+      <c r="T16" s="46">
         <v>112</v>
       </c>
-      <c r="U16" s="52">
+      <c r="U16" s="46">
         <v>57</v>
       </c>
-      <c r="V16" s="52">
+      <c r="V16" s="46">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>46</v>
+      <c r="W16" s="52">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>44</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="31">
+        <v>24</v>
+      </c>
+      <c r="L17" s="27">
         <v>2</v>
       </c>
       <c r="M17" s="18">
         <v>3</v>
       </c>
-      <c r="N17" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="O17" s="33">
+      <c r="N17" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="O17" s="31">
         <v>2</v>
       </c>
-      <c r="P17" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q17" s="31">
+      <c r="P17" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q17" s="27">
         <v>3</v>
       </c>
       <c r="R17" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S17" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="T17" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="U17" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="V17" s="52" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A18" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="S17" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="T17" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="U17" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="V17" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="W17" s="52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="24" x14ac:dyDescent="0.25">
+      <c r="A18" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>49</v>
-      </c>
       <c r="D18" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K18" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="31">
+        <v>24</v>
+      </c>
+      <c r="L18" s="27">
         <v>19</v>
       </c>
       <c r="M18" s="18">
         <v>26</v>
       </c>
-      <c r="N18" s="32">
+      <c r="N18" s="30">
         <v>98</v>
       </c>
-      <c r="O18" s="33">
+      <c r="O18" s="31">
         <v>6</v>
       </c>
-      <c r="P18" s="33">
+      <c r="P18" s="31">
         <v>2</v>
       </c>
-      <c r="Q18" s="31">
+      <c r="Q18" s="27">
         <v>11</v>
       </c>
-      <c r="R18" s="31">
+      <c r="R18" s="27">
         <v>17</v>
       </c>
-      <c r="S18" s="51">
+      <c r="S18" s="33">
         <v>3</v>
       </c>
-      <c r="T18" s="52">
+      <c r="T18" s="46">
         <v>6</v>
       </c>
-      <c r="U18" s="52">
+      <c r="U18" s="46">
         <v>5</v>
       </c>
-      <c r="V18" s="52">
+      <c r="V18" s="46">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="W18" s="52">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>52</v>
-      </c>
       <c r="D19" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I19" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="31">
+        <v>24</v>
+      </c>
+      <c r="L19" s="27">
         <v>2</v>
       </c>
       <c r="M19" s="18">
         <v>5</v>
       </c>
-      <c r="N19" s="32">
+      <c r="N19" s="30">
         <v>0</v>
       </c>
-      <c r="O19" s="33">
+      <c r="O19" s="31">
         <v>1</v>
       </c>
-      <c r="P19" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q19" s="31">
+      <c r="P19" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q19" s="27">
         <v>20</v>
       </c>
-      <c r="R19" s="31">
+      <c r="R19" s="27">
         <v>6</v>
       </c>
-      <c r="S19" s="51">
+      <c r="S19" s="33">
         <v>6</v>
       </c>
-      <c r="T19" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="U19" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="V19" s="52" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
+      <c r="T19" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="U19" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="V19" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="W19" s="52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A20" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="39">
+      <c r="D20" s="34">
         <v>310</v>
       </c>
-      <c r="E20" s="40">
+      <c r="E20" s="35">
         <v>271</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="35">
         <v>301</v>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="27">
         <v>153</v>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="27">
         <v>230</v>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="27">
         <v>381</v>
       </c>
-      <c r="J20" s="31">
+      <c r="J20" s="27">
         <v>297</v>
       </c>
-      <c r="K20" s="31">
+      <c r="K20" s="27">
         <v>271</v>
       </c>
-      <c r="L20" s="31">
+      <c r="L20" s="27">
         <v>44</v>
       </c>
       <c r="M20" s="18">
         <v>55</v>
       </c>
-      <c r="N20" s="32">
-        <v>24</v>
-      </c>
-      <c r="O20" s="33">
+      <c r="N20" s="30">
+        <v>24</v>
+      </c>
+      <c r="O20" s="31">
         <v>39</v>
       </c>
-      <c r="P20" s="33">
+      <c r="P20" s="31">
         <v>27</v>
       </c>
-      <c r="Q20" s="31">
+      <c r="Q20" s="27">
         <v>44</v>
       </c>
-      <c r="R20" s="31">
+      <c r="R20" s="27">
         <v>35</v>
       </c>
-      <c r="S20" s="51">
+      <c r="S20" s="33">
         <v>12</v>
       </c>
-      <c r="T20" s="52">
+      <c r="T20" s="46">
         <v>29</v>
       </c>
-      <c r="U20" s="52">
+      <c r="U20" s="46">
         <v>46</v>
       </c>
-      <c r="V20" s="52">
+      <c r="V20" s="46">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
+      <c r="W20" s="52">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="27" t="s">
         <v>56</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>58</v>
       </c>
       <c r="D21" s="18">
         <v>908</v>
@@ -2063,51 +2130,54 @@
       <c r="K21" s="18">
         <v>599</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="27">
         <v>674</v>
       </c>
       <c r="M21" s="18">
         <v>736</v>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="30">
         <v>716</v>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="31">
         <v>755</v>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="31">
         <v>736</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="27">
         <v>811</v>
       </c>
-      <c r="R21" s="31">
+      <c r="R21" s="27">
         <v>906</v>
       </c>
-      <c r="S21" s="51">
+      <c r="S21" s="33">
         <v>996</v>
       </c>
-      <c r="T21" s="52">
+      <c r="T21" s="46">
         <v>1002</v>
       </c>
-      <c r="U21" s="52">
+      <c r="U21" s="46">
         <v>1021</v>
       </c>
-      <c r="V21" s="52">
+      <c r="V21" s="46">
         <v>1063</v>
       </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="27" t="s">
+      <c r="W21" s="52">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="30">
+      <c r="D22" s="29">
         <v>102</v>
       </c>
       <c r="E22" s="18">
@@ -2116,64 +2186,67 @@
       <c r="F22" s="18">
         <v>144</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="27">
         <v>88</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="27">
         <v>129</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="27">
         <v>241</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="27">
         <v>200</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="27">
         <v>174</v>
       </c>
       <c r="L22" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M22" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N22" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="P22" s="32" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="P22" s="30" t="s">
+        <v>24</v>
       </c>
       <c r="Q22" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="R22" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S22" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="T22" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="U22" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="V22" s="52" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="S22" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="T22" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="U22" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="V22" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="W22" s="52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="17" t="s">
         <v>62</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>64</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
@@ -2190,22 +2263,23 @@
       <c r="P23" s="19"/>
       <c r="Q23" s="19"/>
       <c r="R23" s="19"/>
-      <c r="S23" s="49"/>
-      <c r="T23" s="49"/>
-      <c r="U23" s="49"/>
-      <c r="V23" s="49"/>
-    </row>
-    <row r="24" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S23" s="44"/>
+      <c r="T23" s="44"/>
+      <c r="U23" s="44"/>
+      <c r="V23" s="44"/>
+      <c r="W23" s="50"/>
+    </row>
+    <row r="24" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="23">
+      <c r="D24" s="22">
         <v>1360</v>
       </c>
       <c r="E24" s="14">
@@ -2214,96 +2288,100 @@
       <c r="F24" s="14">
         <v>1303</v>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="23">
         <v>1122</v>
       </c>
-      <c r="H24" s="24">
+      <c r="H24" s="23">
         <v>1207</v>
       </c>
-      <c r="I24" s="24">
+      <c r="I24" s="23">
         <v>1454</v>
       </c>
-      <c r="J24" s="24">
+      <c r="J24" s="23">
         <v>1575</v>
       </c>
-      <c r="K24" s="24">
+      <c r="K24" s="23">
         <v>1265</v>
       </c>
-      <c r="L24" s="24">
+      <c r="L24" s="23">
         <v>1193</v>
       </c>
-      <c r="M24" s="25">
+      <c r="M24" s="24">
         <v>1170</v>
       </c>
-      <c r="N24" s="25">
+      <c r="N24" s="24">
         <v>972</v>
       </c>
-      <c r="O24" s="24">
+      <c r="O24" s="23">
         <v>1107</v>
       </c>
-      <c r="P24" s="24">
+      <c r="P24" s="23">
         <v>1149</v>
       </c>
-      <c r="Q24" s="24">
+      <c r="Q24" s="23">
         <v>1204</v>
       </c>
-      <c r="R24" s="24">
+      <c r="R24" s="23">
         <v>1172</v>
       </c>
-      <c r="S24" s="50">
+      <c r="S24" s="45">
         <v>1075</v>
       </c>
-      <c r="T24" s="55">
+      <c r="T24" s="49">
         <v>1029</v>
       </c>
-      <c r="U24" s="55">
+      <c r="U24" s="49">
         <v>1019</v>
       </c>
-      <c r="V24" s="55">
+      <c r="V24" s="49">
         <v>948</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="27" t="s">
+      <c r="W24" s="56">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A25" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="30"/>
+      <c r="D25" s="29"/>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
       <c r="M25" s="18"/>
       <c r="N25" s="18"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="51"/>
-      <c r="T25" s="52"/>
-      <c r="U25" s="52"/>
-      <c r="V25" s="52"/>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="27" t="s">
+      <c r="O25" s="27"/>
+      <c r="P25" s="27"/>
+      <c r="Q25" s="27"/>
+      <c r="R25" s="27"/>
+      <c r="S25" s="33"/>
+      <c r="T25" s="46"/>
+      <c r="U25" s="46"/>
+      <c r="V25" s="46"/>
+      <c r="W25" s="52"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A26" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="30">
+      <c r="D26" s="29">
         <v>137</v>
       </c>
       <c r="E26" s="18">
@@ -2312,22 +2390,22 @@
       <c r="F26" s="18">
         <v>101</v>
       </c>
-      <c r="G26" s="31">
+      <c r="G26" s="27">
         <v>91</v>
       </c>
-      <c r="H26" s="31">
+      <c r="H26" s="27">
         <v>78</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="27">
         <v>61</v>
       </c>
-      <c r="J26" s="31">
+      <c r="J26" s="27">
         <v>133</v>
       </c>
-      <c r="K26" s="31">
+      <c r="K26" s="27">
         <v>97</v>
       </c>
-      <c r="L26" s="31">
+      <c r="L26" s="27">
         <v>44</v>
       </c>
       <c r="M26" s="18">
@@ -2336,42 +2414,45 @@
       <c r="N26" s="18">
         <v>49</v>
       </c>
-      <c r="O26" s="31">
+      <c r="O26" s="27">
         <v>90</v>
       </c>
-      <c r="P26" s="31">
+      <c r="P26" s="27">
         <v>147</v>
       </c>
-      <c r="Q26" s="31">
+      <c r="Q26" s="27">
         <v>118</v>
       </c>
-      <c r="R26" s="31">
+      <c r="R26" s="27">
         <v>110</v>
       </c>
-      <c r="S26" s="51">
+      <c r="S26" s="33">
         <v>93</v>
       </c>
-      <c r="T26" s="52">
+      <c r="T26" s="46">
         <v>51</v>
       </c>
-      <c r="U26" s="52">
+      <c r="U26" s="46">
         <v>15</v>
       </c>
-      <c r="V26" s="52">
+      <c r="V26" s="46">
         <v>16</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="27" t="s">
+      <c r="W26" s="52">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="30">
+      <c r="D27" s="29">
         <v>41</v>
       </c>
       <c r="E27" s="18">
@@ -2380,22 +2461,22 @@
       <c r="F27" s="18">
         <v>64</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="27">
         <v>65</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="27">
         <v>46</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="27">
         <v>114</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="27">
         <v>77</v>
       </c>
-      <c r="K27" s="31">
-        <v>24</v>
-      </c>
-      <c r="L27" s="31">
+      <c r="K27" s="27">
+        <v>24</v>
+      </c>
+      <c r="L27" s="27">
         <v>32</v>
       </c>
       <c r="M27" s="18">
@@ -2404,94 +2485,100 @@
       <c r="N27" s="18">
         <v>19</v>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="27">
         <v>18</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="27">
         <v>22</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="27">
         <v>30</v>
       </c>
-      <c r="R27" s="31">
+      <c r="R27" s="27">
         <v>8</v>
       </c>
-      <c r="S27" s="51">
+      <c r="S27" s="33">
         <v>14</v>
       </c>
-      <c r="T27" s="52">
+      <c r="T27" s="46">
         <v>4</v>
       </c>
-      <c r="U27" s="52">
+      <c r="U27" s="46">
         <v>30</v>
       </c>
-      <c r="V27" s="52">
+      <c r="V27" s="46">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A28" s="34" t="s">
+      <c r="W27" s="52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="24" x14ac:dyDescent="0.25">
+      <c r="A28" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="30"/>
+      <c r="D28" s="29"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31">
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27">
         <v>5</v>
       </c>
       <c r="M28" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N28" s="18">
         <v>3</v>
       </c>
-      <c r="O28" s="31">
+      <c r="O28" s="27">
         <v>6</v>
       </c>
-      <c r="P28" s="32" t="s">
+      <c r="P28" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q28" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="R28" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="S28" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="T28" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="U28" s="46">
+        <v>1</v>
+      </c>
+      <c r="V28" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="W28" s="52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A29" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="Q28" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="R28" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S28" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="T28" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="U28" s="52">
-        <v>1</v>
-      </c>
-      <c r="V28" s="52" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A29" s="27" t="s">
+      <c r="C29" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="30">
+      <c r="D29" s="29">
         <v>116</v>
       </c>
       <c r="E29" s="18">
@@ -2500,22 +2587,22 @@
       <c r="F29" s="18">
         <v>83</v>
       </c>
-      <c r="G29" s="31">
+      <c r="G29" s="27">
         <v>317</v>
       </c>
-      <c r="H29" s="31">
+      <c r="H29" s="27">
         <v>215</v>
       </c>
-      <c r="I29" s="31">
+      <c r="I29" s="27">
         <v>237</v>
       </c>
-      <c r="J29" s="31">
+      <c r="J29" s="27">
         <v>286</v>
       </c>
-      <c r="K29" s="31">
+      <c r="K29" s="27">
         <v>230</v>
       </c>
-      <c r="L29" s="31">
+      <c r="L29" s="27">
         <v>89</v>
       </c>
       <c r="M29" s="18">
@@ -2524,42 +2611,45 @@
       <c r="N29" s="18">
         <v>132</v>
       </c>
-      <c r="O29" s="31">
+      <c r="O29" s="27">
         <v>194</v>
       </c>
-      <c r="P29" s="31">
+      <c r="P29" s="27">
         <v>220</v>
       </c>
-      <c r="Q29" s="31">
+      <c r="Q29" s="27">
         <v>272</v>
       </c>
-      <c r="R29" s="31">
+      <c r="R29" s="27">
         <v>260</v>
       </c>
-      <c r="S29" s="51">
+      <c r="S29" s="33">
         <v>139</v>
       </c>
-      <c r="T29" s="52">
+      <c r="T29" s="46">
         <v>127</v>
       </c>
-      <c r="U29" s="52">
+      <c r="U29" s="46">
         <v>179</v>
       </c>
-      <c r="V29" s="52">
+      <c r="V29" s="46">
         <v>111</v>
       </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
+      <c r="W29" s="52">
         <v>30</v>
       </c>
-      <c r="B30" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="30">
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A30" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="29">
         <v>64</v>
       </c>
       <c r="E30" s="18">
@@ -2568,22 +2658,22 @@
       <c r="F30" s="18">
         <v>55</v>
       </c>
-      <c r="G30" s="31">
+      <c r="G30" s="27">
         <v>64</v>
       </c>
-      <c r="H30" s="31">
+      <c r="H30" s="27">
         <v>78</v>
       </c>
-      <c r="I30" s="31">
+      <c r="I30" s="27">
         <v>127</v>
       </c>
-      <c r="J30" s="31">
+      <c r="J30" s="27">
         <v>46</v>
       </c>
-      <c r="K30" s="31">
+      <c r="K30" s="27">
         <v>31</v>
       </c>
-      <c r="L30" s="31">
+      <c r="L30" s="27">
         <v>46</v>
       </c>
       <c r="M30" s="18">
@@ -2592,42 +2682,45 @@
       <c r="N30" s="18">
         <v>41</v>
       </c>
-      <c r="O30" s="31">
+      <c r="O30" s="27">
         <v>12</v>
       </c>
-      <c r="P30" s="31">
+      <c r="P30" s="27">
         <v>10</v>
       </c>
-      <c r="Q30" s="31">
+      <c r="Q30" s="27">
         <v>73</v>
       </c>
-      <c r="R30" s="31">
+      <c r="R30" s="27">
         <v>33</v>
       </c>
-      <c r="S30" s="51">
+      <c r="S30" s="33">
         <v>23</v>
       </c>
-      <c r="T30" s="52">
+      <c r="T30" s="46">
         <v>14</v>
       </c>
-      <c r="U30" s="52">
+      <c r="U30" s="46">
         <v>16</v>
       </c>
-      <c r="V30" s="52">
+      <c r="V30" s="46">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A31" s="27" t="s">
+      <c r="W30" s="52">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A31" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" s="30">
+      <c r="D31" s="29">
         <v>31</v>
       </c>
       <c r="E31" s="18">
@@ -2636,22 +2729,22 @@
       <c r="F31" s="18">
         <v>39</v>
       </c>
-      <c r="G31" s="31">
-        <v>24</v>
-      </c>
-      <c r="H31" s="31">
+      <c r="G31" s="27">
+        <v>24</v>
+      </c>
+      <c r="H31" s="27">
         <v>7</v>
       </c>
-      <c r="I31" s="31">
+      <c r="I31" s="27">
         <v>13</v>
       </c>
-      <c r="J31" s="31">
+      <c r="J31" s="27">
         <v>36</v>
       </c>
-      <c r="K31" s="31">
+      <c r="K31" s="27">
         <v>13</v>
       </c>
-      <c r="L31" s="31">
+      <c r="L31" s="27">
         <v>10</v>
       </c>
       <c r="M31" s="18">
@@ -2660,42 +2753,45 @@
       <c r="N31" s="18">
         <v>9</v>
       </c>
-      <c r="O31" s="31">
+      <c r="O31" s="27">
         <v>5</v>
       </c>
-      <c r="P31" s="31">
+      <c r="P31" s="27">
         <v>11</v>
       </c>
-      <c r="Q31" s="31">
+      <c r="Q31" s="27">
         <v>10</v>
       </c>
-      <c r="R31" s="31">
+      <c r="R31" s="27">
         <v>17</v>
       </c>
-      <c r="S31" s="51">
+      <c r="S31" s="33">
         <v>14</v>
       </c>
-      <c r="T31" s="52">
+      <c r="T31" s="46">
         <v>12</v>
       </c>
-      <c r="U31" s="52">
+      <c r="U31" s="46">
         <v>8</v>
       </c>
-      <c r="V31" s="52">
+      <c r="V31" s="46">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A32" s="27" t="s">
+      <c r="W31" s="52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A32" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="30">
+      <c r="D32" s="29">
         <v>14</v>
       </c>
       <c r="E32" s="18">
@@ -2704,118 +2800,124 @@
       <c r="F32" s="18">
         <v>2</v>
       </c>
-      <c r="G32" s="31">
+      <c r="G32" s="27">
         <v>6</v>
       </c>
-      <c r="H32" s="31">
+      <c r="H32" s="27">
         <v>20</v>
       </c>
-      <c r="I32" s="31">
+      <c r="I32" s="27">
         <v>21</v>
       </c>
-      <c r="J32" s="31">
+      <c r="J32" s="27">
         <v>1</v>
       </c>
-      <c r="K32" s="31">
+      <c r="K32" s="27">
         <v>1</v>
       </c>
-      <c r="L32" s="31">
+      <c r="L32" s="27">
         <v>3</v>
       </c>
       <c r="M32" s="18">
         <v>1</v>
       </c>
       <c r="N32" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="O32" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P32" s="18">
         <v>1</v>
       </c>
       <c r="Q32" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="R32" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S32" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="T32" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="U32" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="V32" s="52" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="S32" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="T32" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="U32" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="V32" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="W32" s="52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" ht="24" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="30"/>
+      <c r="D33" s="29"/>
       <c r="E33" s="18"/>
       <c r="F33" s="18"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31">
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="27"/>
+      <c r="K33" s="27"/>
+      <c r="L33" s="27">
         <v>4</v>
       </c>
       <c r="M33" s="18">
         <v>3</v>
       </c>
       <c r="N33" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="O33" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="P33" s="32" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="P33" s="30" t="s">
+        <v>24</v>
       </c>
       <c r="Q33" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="R33" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S33" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="T33" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="U33" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="V33" s="52" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A34" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="S33" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="T33" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="U33" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="V33" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="W33" s="52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="30">
+      <c r="D34" s="29">
         <v>39</v>
       </c>
       <c r="E34" s="18">
@@ -2824,22 +2926,22 @@
       <c r="F34" s="18">
         <v>94</v>
       </c>
-      <c r="G34" s="31">
+      <c r="G34" s="27">
         <v>40</v>
       </c>
-      <c r="H34" s="31">
+      <c r="H34" s="27">
         <v>66</v>
       </c>
-      <c r="I34" s="31">
+      <c r="I34" s="27">
         <v>74</v>
       </c>
-      <c r="J34" s="31">
+      <c r="J34" s="27">
         <v>115</v>
       </c>
-      <c r="K34" s="31">
+      <c r="K34" s="27">
         <v>88</v>
       </c>
-      <c r="L34" s="31">
+      <c r="L34" s="27">
         <v>380</v>
       </c>
       <c r="M34" s="18">
@@ -2848,101 +2950,107 @@
       <c r="N34" s="18">
         <v>60</v>
       </c>
-      <c r="O34" s="31">
+      <c r="O34" s="27">
         <v>204</v>
       </c>
-      <c r="P34" s="31">
+      <c r="P34" s="27">
         <v>199</v>
       </c>
-      <c r="Q34" s="31">
+      <c r="Q34" s="27">
         <v>121</v>
       </c>
-      <c r="R34" s="31">
+      <c r="R34" s="27">
         <v>91</v>
       </c>
-      <c r="S34" s="51">
+      <c r="S34" s="33">
         <v>75</v>
       </c>
-      <c r="T34" s="52">
+      <c r="T34" s="46">
         <v>70</v>
       </c>
-      <c r="U34" s="52">
+      <c r="U34" s="46">
         <v>46</v>
       </c>
-      <c r="V34" s="52">
+      <c r="V34" s="46">
         <v>9</v>
       </c>
-    </row>
-    <row r="35" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A35" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="D35" s="30"/>
+      <c r="W34" s="52">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="29"/>
       <c r="E35" s="18"/>
       <c r="F35" s="18"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="27"/>
+      <c r="K35" s="27"/>
       <c r="L35" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M35" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N35" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="O35" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="P35" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q35" s="31">
+        <v>24</v>
+      </c>
+      <c r="P35" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q35" s="27">
         <v>2</v>
       </c>
       <c r="R35" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S35" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="T35" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="U35" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="V35" s="52" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A36" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="S35" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="T35" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="U35" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="V35" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="W35" s="52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" ht="24" x14ac:dyDescent="0.25">
+      <c r="A36" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="D36" s="30"/>
+      <c r="D36" s="29"/>
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="27"/>
       <c r="L36" s="18">
         <v>4</v>
       </c>
@@ -2953,50 +3061,53 @@
         <v>79</v>
       </c>
       <c r="O36" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P36" s="18">
         <v>1</v>
       </c>
-      <c r="Q36" s="31">
+      <c r="Q36" s="27">
         <v>4</v>
       </c>
-      <c r="R36" s="31">
+      <c r="R36" s="27">
         <v>8</v>
       </c>
-      <c r="S36" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="T36" s="52">
+      <c r="S36" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="T36" s="46">
         <v>3</v>
       </c>
-      <c r="U36" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="V36" s="52">
+      <c r="U36" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="V36" s="46">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A37" s="27" t="s">
+      <c r="W36" s="53">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A37" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="B37" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" s="30"/>
+      <c r="D37" s="29"/>
       <c r="E37" s="18"/>
       <c r="F37" s="18"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="27"/>
+      <c r="K37" s="27"/>
       <c r="L37" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M37" s="18">
         <v>4</v>
@@ -3005,65 +3116,68 @@
         <v>2</v>
       </c>
       <c r="O37" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P37" s="18">
         <v>1</v>
       </c>
-      <c r="Q37" s="31">
+      <c r="Q37" s="27">
         <v>18</v>
       </c>
-      <c r="R37" s="31">
+      <c r="R37" s="27">
         <v>3</v>
       </c>
-      <c r="S37" s="51">
+      <c r="S37" s="33">
         <v>3</v>
       </c>
-      <c r="T37" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="U37" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="V37" s="52" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A38" s="27" t="s">
+      <c r="T37" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="U37" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="V37" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="W37" s="52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B38" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="D38" s="39">
+      <c r="D38" s="34">
         <v>196</v>
       </c>
-      <c r="E38" s="40">
+      <c r="E38" s="35">
         <v>213</v>
       </c>
-      <c r="F38" s="40">
+      <c r="F38" s="35">
         <v>219</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="27">
         <v>99</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="27">
         <v>195</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="27">
         <v>260</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="27">
         <v>233</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="27">
         <v>213</v>
       </c>
-      <c r="L38" s="31">
+      <c r="L38" s="27">
         <v>45</v>
       </c>
       <c r="M38" s="18">
@@ -3072,40 +3186,43 @@
       <c r="N38" s="18">
         <v>14</v>
       </c>
-      <c r="O38" s="31">
+      <c r="O38" s="27">
         <v>36</v>
       </c>
-      <c r="P38" s="31">
+      <c r="P38" s="27">
         <v>20</v>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="27">
         <v>31</v>
       </c>
-      <c r="R38" s="31">
+      <c r="R38" s="27">
         <v>27</v>
       </c>
-      <c r="S38" s="51">
+      <c r="S38" s="33">
         <v>9</v>
       </c>
-      <c r="T38" s="52">
+      <c r="T38" s="46">
         <v>16</v>
       </c>
-      <c r="U38" s="52">
+      <c r="U38" s="46">
         <v>25</v>
       </c>
-      <c r="V38" s="52">
+      <c r="V38" s="46">
         <v>7</v>
       </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A39" s="27" t="s">
+      <c r="W38" s="52">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="27" t="s">
         <v>56</v>
-      </c>
-      <c r="B39" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" s="38" t="s">
-        <v>58</v>
       </c>
       <c r="D39" s="18">
         <v>658</v>
@@ -3131,7 +3248,7 @@
       <c r="K39" s="18">
         <v>410</v>
       </c>
-      <c r="L39" s="31">
+      <c r="L39" s="27">
         <v>531</v>
       </c>
       <c r="M39" s="18">
@@ -3140,124 +3257,130 @@
       <c r="N39" s="18">
         <v>564</v>
       </c>
-      <c r="O39" s="31">
+      <c r="O39" s="27">
         <v>542</v>
       </c>
-      <c r="P39" s="31">
+      <c r="P39" s="27">
         <v>517</v>
       </c>
-      <c r="Q39" s="31">
+      <c r="Q39" s="27">
         <v>525</v>
       </c>
-      <c r="R39" s="31">
+      <c r="R39" s="27">
         <v>615</v>
       </c>
-      <c r="S39" s="51">
+      <c r="S39" s="33">
         <v>705</v>
       </c>
-      <c r="T39" s="52">
+      <c r="T39" s="46">
         <v>732</v>
       </c>
-      <c r="U39" s="52">
+      <c r="U39" s="46">
         <v>699</v>
       </c>
-      <c r="V39" s="52">
+      <c r="V39" s="46">
         <v>783</v>
       </c>
-    </row>
-    <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="41" t="s">
+      <c r="W39" s="52">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="D40" s="44">
+      <c r="D40" s="39">
         <v>64</v>
       </c>
-      <c r="E40" s="45">
+      <c r="E40" s="40">
         <v>108</v>
       </c>
-      <c r="F40" s="45">
+      <c r="F40" s="40">
         <v>111</v>
       </c>
-      <c r="G40" s="42">
+      <c r="G40" s="37">
         <v>67</v>
       </c>
-      <c r="H40" s="42">
+      <c r="H40" s="37">
         <v>111</v>
       </c>
-      <c r="I40" s="42">
+      <c r="I40" s="37">
         <v>154</v>
       </c>
-      <c r="J40" s="42">
+      <c r="J40" s="37">
         <v>133</v>
       </c>
-      <c r="K40" s="42">
+      <c r="K40" s="37">
         <v>158</v>
       </c>
-      <c r="L40" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="M40" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="N40" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="O40" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="P40" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q40" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="R40" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="S40" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="T40" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="U40" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="V40" s="53" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A41" s="46" t="s">
+      <c r="L40" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="M40" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="N40" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="O40" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="P40" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q40" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="R40" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="S40" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="T40" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="U40" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="V40" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="W40" s="51" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A41" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="42" t="s">
         <v>65</v>
-      </c>
-      <c r="B41" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="47" t="s">
-        <v>67</v>
       </c>
       <c r="D41" s="18"/>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="31"/>
-      <c r="M41" s="31"/>
-      <c r="N41" s="31"/>
-      <c r="O41" s="31"/>
-      <c r="P41" s="31"/>
-      <c r="Q41" s="31"/>
-      <c r="R41" s="31"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="27"/>
+      <c r="K41" s="27"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="27"/>
+      <c r="N41" s="27"/>
+      <c r="O41" s="27"/>
+      <c r="P41" s="27"/>
+      <c r="Q41" s="27"/>
+      <c r="R41" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
